--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/145.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/145.xlsx
@@ -426,13 +426,13 @@
         <v>0.2832410924148839</v>
       </c>
       <c r="E2">
-        <v>-3.564762473857615</v>
+        <v>-4.600510520417972</v>
       </c>
       <c r="F2">
-        <v>-3.773056459502409</v>
+        <v>-2.998262390050841</v>
       </c>
       <c r="G2">
-        <v>-2.113529565486463</v>
+        <v>-2.013266383284096</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>1.083003264955607</v>
       </c>
       <c r="E3">
-        <v>-4.500553513646664</v>
+        <v>-5.52419242071051</v>
       </c>
       <c r="F3">
-        <v>-4.370036779886181</v>
+        <v>-2.888382498078779</v>
       </c>
       <c r="G3">
-        <v>-1.251728350703388</v>
+        <v>-2.409909465435255</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>1.862735324573285</v>
       </c>
       <c r="E4">
-        <v>-5.207996251598935</v>
+        <v>-4.566406582666207</v>
       </c>
       <c r="F4">
-        <v>-4.26870969171045</v>
+        <v>-3.009029214716956</v>
       </c>
       <c r="G4">
-        <v>-0.7298274675283635</v>
+        <v>-1.247090276402869</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.523684964506027</v>
       </c>
       <c r="E5">
-        <v>-4.362068250018097</v>
+        <v>-6.246198731071448</v>
       </c>
       <c r="F5">
-        <v>-4.496613683324721</v>
+        <v>-2.716579704813034</v>
       </c>
       <c r="G5">
-        <v>-0.8267205143717525</v>
+        <v>-1.328566112669872</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.09281891031211</v>
       </c>
       <c r="E6">
-        <v>-5.529264311599101</v>
+        <v>-6.825766419995124</v>
       </c>
       <c r="F6">
-        <v>-4.710652329649321</v>
+        <v>-2.503971936783035</v>
       </c>
       <c r="G6">
-        <v>-0.9591324043059822</v>
+        <v>-2.293848359919486</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.564327533904797</v>
       </c>
       <c r="E7">
-        <v>-5.171374482298905</v>
+        <v>-7.107804309666841</v>
       </c>
       <c r="F7">
-        <v>-4.532325459864923</v>
+        <v>-2.798127097957885</v>
       </c>
       <c r="G7">
-        <v>-0.7978128307228366</v>
+        <v>-1.719409119036228</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.96255852688508</v>
       </c>
       <c r="E8">
-        <v>-6.618000032523208</v>
+        <v>-8.347193303878127</v>
       </c>
       <c r="F8">
-        <v>-4.700130187547141</v>
+        <v>-2.972809068577898</v>
       </c>
       <c r="G8">
-        <v>-0.7458604395750538</v>
+        <v>-1.087270379949013</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.310338831101183</v>
       </c>
       <c r="E9">
-        <v>-7.52822330806495</v>
+        <v>-8.572493942707743</v>
       </c>
       <c r="F9">
-        <v>-4.830393166503867</v>
+        <v>-2.920806501138528</v>
       </c>
       <c r="G9">
-        <v>0.1185296218197317</v>
+        <v>-2.070840080757561</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.633669024726682</v>
       </c>
       <c r="E10">
-        <v>-8.559257213183322</v>
+        <v>-10.13760248686873</v>
       </c>
       <c r="F10">
-        <v>-4.793243384992445</v>
+        <v>-3.102273859753242</v>
       </c>
       <c r="G10">
-        <v>-0.1599336056705249</v>
+        <v>0.195026397595671</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.955711414551508</v>
       </c>
       <c r="E11">
-        <v>-8.880380362015242</v>
+        <v>-12.33337802065595</v>
       </c>
       <c r="F11">
-        <v>-4.419252024914377</v>
+        <v>-2.991549060675293</v>
       </c>
       <c r="G11">
-        <v>0.615932468004149</v>
+        <v>-0.4319015428127315</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.300373190408277</v>
       </c>
       <c r="E12">
-        <v>-9.319664983129305</v>
+        <v>-12.01627615674284</v>
       </c>
       <c r="F12">
-        <v>-4.575715834536133</v>
+        <v>-2.951495554367914</v>
       </c>
       <c r="G12">
-        <v>0.5382174114697579</v>
+        <v>0.02862513660974404</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.671407834008495</v>
       </c>
       <c r="E13">
-        <v>-10.80736832107719</v>
+        <v>-13.07338954367139</v>
       </c>
       <c r="F13">
-        <v>-4.152252669071568</v>
+        <v>-2.918385806646779</v>
       </c>
       <c r="G13">
-        <v>0.8177300818959634</v>
+        <v>-0.7408317209009009</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.071160446459738</v>
       </c>
       <c r="E14">
-        <v>-11.94855735643214</v>
+        <v>-13.45849097328367</v>
       </c>
       <c r="F14">
-        <v>-4.272408436875959</v>
+        <v>-2.522239192664671</v>
       </c>
       <c r="G14">
-        <v>0.5076445234145884</v>
+        <v>0.5276633922905614</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.490683576853056</v>
       </c>
       <c r="E15">
-        <v>-12.39157796860253</v>
+        <v>-14.84083030649509</v>
       </c>
       <c r="F15">
-        <v>-4.098421713152824</v>
+        <v>-2.148604958270535</v>
       </c>
       <c r="G15">
-        <v>1.727107146623905</v>
+        <v>0.9048669510351204</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.903932754376564</v>
       </c>
       <c r="E16">
-        <v>-14.13074746819635</v>
+        <v>-15.13684306695448</v>
       </c>
       <c r="F16">
-        <v>-3.493411211924815</v>
+        <v>-1.267864130487899</v>
       </c>
       <c r="G16">
-        <v>1.875545387513747</v>
+        <v>2.482156509947642</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.288997141362975</v>
       </c>
       <c r="E17">
-        <v>-14.18195545227508</v>
+        <v>-15.9360009889841</v>
       </c>
       <c r="F17">
-        <v>-3.335570370009585</v>
+        <v>-2.000285356318927</v>
       </c>
       <c r="G17">
-        <v>2.149711526894029</v>
+        <v>1.382522393077785</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.615024073287295</v>
       </c>
       <c r="E18">
-        <v>-15.83306877478975</v>
+        <v>-16.90941459082887</v>
       </c>
       <c r="F18">
-        <v>-3.020934723936272</v>
+        <v>-1.390673397553609</v>
       </c>
       <c r="G18">
-        <v>3.051494200154883</v>
+        <v>2.523061610630877</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.847254019802601</v>
       </c>
       <c r="E19">
-        <v>-15.90064266393221</v>
+        <v>-17.40343034879964</v>
       </c>
       <c r="F19">
-        <v>-3.31465278227846</v>
+        <v>-1.435569876550402</v>
       </c>
       <c r="G19">
-        <v>2.971458451197463</v>
+        <v>2.175593371920051</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.963757275444971</v>
       </c>
       <c r="E20">
-        <v>-18.17533138577709</v>
+        <v>-19.58735939458279</v>
       </c>
       <c r="F20">
-        <v>-2.191267620073601</v>
+        <v>-0.3976185218068806</v>
       </c>
       <c r="G20">
-        <v>3.558540665495197</v>
+        <v>2.768435935456118</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.942007852685481</v>
       </c>
       <c r="E21">
-        <v>-19.03447800298632</v>
+        <v>-20.31038914006946</v>
       </c>
       <c r="F21">
-        <v>-1.931131253815348</v>
+        <v>-0.5212687367136886</v>
       </c>
       <c r="G21">
-        <v>3.284904213401198</v>
+        <v>2.848789496785308</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.767975541295004</v>
       </c>
       <c r="E22">
-        <v>-18.5030615781862</v>
+        <v>-20.38914836001086</v>
       </c>
       <c r="F22">
-        <v>-1.523380034737857</v>
+        <v>-0.08987595573051801</v>
       </c>
       <c r="G22">
-        <v>4.013697640052975</v>
+        <v>3.383028783185196</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.438350492267528</v>
       </c>
       <c r="E23">
-        <v>-18.92423230326958</v>
+        <v>-22.9186226149493</v>
       </c>
       <c r="F23">
-        <v>-1.735849228500256</v>
+        <v>0.296023289125739</v>
       </c>
       <c r="G23">
-        <v>3.029134775582645</v>
+        <v>3.099013770825581</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.951471168141312</v>
       </c>
       <c r="E24">
-        <v>-19.38819257925144</v>
+        <v>-21.22448426088776</v>
       </c>
       <c r="F24">
-        <v>-1.238181522367775</v>
+        <v>0.4607382065669341</v>
       </c>
       <c r="G24">
-        <v>3.768002192310424</v>
+        <v>3.851272344259713</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.318116170731377</v>
       </c>
       <c r="E25">
-        <v>-20.04632476373419</v>
+        <v>-21.00205920305302</v>
       </c>
       <c r="F25">
-        <v>-0.977513030921935</v>
+        <v>0.3126316130609524</v>
       </c>
       <c r="G25">
-        <v>3.368508730449952</v>
+        <v>2.035116993052157</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.553718218104539</v>
       </c>
       <c r="E26">
-        <v>-18.85677162597732</v>
+        <v>-21.84369873974859</v>
       </c>
       <c r="F26">
-        <v>-1.202869631571222</v>
+        <v>0.499679159468717</v>
       </c>
       <c r="G26">
-        <v>2.503479733766087</v>
+        <v>2.439116107391577</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.674824620850878</v>
       </c>
       <c r="E27">
-        <v>-21.16555070015194</v>
+        <v>-21.72614408298348</v>
       </c>
       <c r="F27">
-        <v>-0.6629383575263667</v>
+        <v>0.9795475948175736</v>
       </c>
       <c r="G27">
-        <v>2.45513914780165</v>
+        <v>2.948877220074094</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.710518721817643</v>
       </c>
       <c r="E28">
-        <v>-20.31925136370247</v>
+        <v>-21.99975448252692</v>
       </c>
       <c r="F28">
-        <v>-0.7987688546288194</v>
+        <v>0.9134152032006532</v>
       </c>
       <c r="G28">
-        <v>2.2614060228435</v>
+        <v>2.212744313961752</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.688715619746003</v>
       </c>
       <c r="E29">
-        <v>-20.94919832596148</v>
+        <v>-21.42139589616329</v>
       </c>
       <c r="F29">
-        <v>-0.8121384999669592</v>
+        <v>0.7651502391031275</v>
       </c>
       <c r="G29">
-        <v>1.971521413242758</v>
+        <v>2.989441334566783</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.637301687219513</v>
       </c>
       <c r="E30">
-        <v>-20.19775240607668</v>
+        <v>-21.85275115928992</v>
       </c>
       <c r="F30">
-        <v>-0.4816000709437613</v>
+        <v>0.2027540966477636</v>
       </c>
       <c r="G30">
-        <v>1.764757981042036</v>
+        <v>1.621116720638599</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.5945335065483609</v>
       </c>
       <c r="E31">
-        <v>-19.43125383859038</v>
+        <v>-21.17340760255525</v>
       </c>
       <c r="F31">
-        <v>-0.5392002469412517</v>
+        <v>0.7941273062379232</v>
       </c>
       <c r="G31">
-        <v>1.307578263159764</v>
+        <v>2.079706730920601</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4061743641899678</v>
       </c>
       <c r="E32">
-        <v>-19.51187878982294</v>
+        <v>-20.21843847534371</v>
       </c>
       <c r="F32">
-        <v>-0.7922954566994607</v>
+        <v>0.4671427132889713</v>
       </c>
       <c r="G32">
-        <v>0.7167485113115745</v>
+        <v>0.7363668041772955</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.332410197385864</v>
       </c>
       <c r="E33">
-        <v>-18.02850467302639</v>
+        <v>-21.22530844315716</v>
       </c>
       <c r="F33">
-        <v>-0.9626729146413096</v>
+        <v>0.1807318740406204</v>
       </c>
       <c r="G33">
-        <v>0.584608086111565</v>
+        <v>1.883202679346081</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.143954223618683</v>
       </c>
       <c r="E34">
-        <v>-18.02067494146713</v>
+        <v>-19.02427082257303</v>
       </c>
       <c r="F34">
-        <v>-0.8590684573591764</v>
+        <v>0.4225629754752663</v>
       </c>
       <c r="G34">
-        <v>0.610377372589252</v>
+        <v>0.4542619765938405</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.809730587396873</v>
       </c>
       <c r="E35">
-        <v>-17.50422512326237</v>
+        <v>-20.16824034096869</v>
       </c>
       <c r="F35">
-        <v>-1.190587992196989</v>
+        <v>0.08402762343205683</v>
       </c>
       <c r="G35">
-        <v>0.6947830416585101</v>
+        <v>1.008897534061178</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.307057973002377</v>
       </c>
       <c r="E36">
-        <v>-17.05352874764897</v>
+        <v>-18.50580130496084</v>
       </c>
       <c r="F36">
-        <v>-0.6062282242533532</v>
+        <v>-0.04440696704529376</v>
       </c>
       <c r="G36">
-        <v>1.489343765993449</v>
+        <v>0.9389059802699067</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.612972999887528</v>
       </c>
       <c r="E37">
-        <v>-15.53089276120592</v>
+        <v>-18.19004892630202</v>
       </c>
       <c r="F37">
-        <v>-1.130331149526349</v>
+        <v>0.01432793424060903</v>
       </c>
       <c r="G37">
-        <v>0.7318578411528082</v>
+        <v>1.287969901930661</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.720220895623155</v>
       </c>
       <c r="E38">
-        <v>-15.59766511044902</v>
+        <v>-18.56844368590894</v>
       </c>
       <c r="F38">
-        <v>-1.025943549669031</v>
+        <v>0.2937886800790539</v>
       </c>
       <c r="G38">
-        <v>0.5810691129300841</v>
+        <v>0.6041204415200294</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.635506844060201</v>
       </c>
       <c r="E39">
-        <v>-15.50086445006106</v>
+        <v>-16.14751242446036</v>
       </c>
       <c r="F39">
-        <v>-1.033796355450737</v>
+        <v>0.2297135224462893</v>
       </c>
       <c r="G39">
-        <v>0.4520008739905184</v>
+        <v>2.191394605778993</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.370087544805122</v>
       </c>
       <c r="E40">
-        <v>-14.42581377758813</v>
+        <v>-16.25229225604983</v>
       </c>
       <c r="F40">
-        <v>-1.596864781067205</v>
+        <v>0.6763122557765517</v>
       </c>
       <c r="G40">
-        <v>1.181813948668391</v>
+        <v>1.049829119108727</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.947103544731787</v>
       </c>
       <c r="E41">
-        <v>-14.48428996244918</v>
+        <v>-15.22657477941646</v>
       </c>
       <c r="F41">
-        <v>-1.642203114014406</v>
+        <v>-0.04546329889089187</v>
       </c>
       <c r="G41">
-        <v>1.372709936099385</v>
+        <v>1.612261011321048</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.398190383848967</v>
       </c>
       <c r="E42">
-        <v>-13.36595613541094</v>
+        <v>-14.44227930908002</v>
       </c>
       <c r="F42">
-        <v>-1.572394149114793</v>
+        <v>0.1374206846651824</v>
       </c>
       <c r="G42">
-        <v>0.7526182722295778</v>
+        <v>1.963208633393648</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.754270805069539</v>
       </c>
       <c r="E43">
-        <v>-13.73299348220663</v>
+        <v>-13.78327312911379</v>
       </c>
       <c r="F43">
-        <v>-1.559972351767043</v>
+        <v>-0.3620437358283642</v>
       </c>
       <c r="G43">
-        <v>1.4679443996276</v>
+        <v>2.945036987248539</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.048590868512834</v>
       </c>
       <c r="E44">
-        <v>-12.90539221493483</v>
+        <v>-13.01578282581981</v>
       </c>
       <c r="F44">
-        <v>-1.049924024640615</v>
+        <v>-0.1186186343898285</v>
       </c>
       <c r="G44">
-        <v>1.242727986590981</v>
+        <v>1.955296429554789</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.317580052544027</v>
       </c>
       <c r="E45">
-        <v>-11.62071395217284</v>
+        <v>-13.42486705377672</v>
       </c>
       <c r="F45">
-        <v>-1.410524359350685</v>
+        <v>-0.3364803467942984</v>
       </c>
       <c r="G45">
-        <v>2.197022533195754</v>
+        <v>1.756842466657639</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.4074984876798492</v>
       </c>
       <c r="E46">
-        <v>-10.11883649058095</v>
+        <v>-13.16846032698842</v>
       </c>
       <c r="F46">
-        <v>-1.067229179178622</v>
+        <v>-0.2586309069619992</v>
       </c>
       <c r="G46">
-        <v>1.580261278138453</v>
+        <v>2.441999592556282</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.099560895435926</v>
       </c>
       <c r="E47">
-        <v>-11.33695977085221</v>
+        <v>-12.02391116391977</v>
       </c>
       <c r="F47">
-        <v>-1.603225735876568</v>
+        <v>-0.3874012430934229</v>
       </c>
       <c r="G47">
-        <v>2.347284884677733</v>
+        <v>2.159712684968167</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.732556777895906</v>
       </c>
       <c r="E48">
-        <v>-9.864200397129643</v>
+        <v>-10.9482446189818</v>
       </c>
       <c r="F48">
-        <v>-2.012015074181629</v>
+        <v>-0.3528780378427585</v>
       </c>
       <c r="G48">
-        <v>2.822851372485118</v>
+        <v>2.76492675718449</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.289304128589698</v>
       </c>
       <c r="E49">
-        <v>-9.812716176136439</v>
+        <v>-10.50245258071872</v>
       </c>
       <c r="F49">
-        <v>-1.814415295259291</v>
+        <v>-0.5024677719385492</v>
       </c>
       <c r="G49">
-        <v>2.70841905537467</v>
+        <v>1.612039204769917</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.75891309128599</v>
       </c>
       <c r="E50">
-        <v>-10.36389486150603</v>
+        <v>-10.69061067573742</v>
       </c>
       <c r="F50">
-        <v>-1.617769699151006</v>
+        <v>-0.2118838676030153</v>
       </c>
       <c r="G50">
-        <v>2.545066806830412</v>
+        <v>2.378493397476443</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.131258517262806</v>
       </c>
       <c r="E51">
-        <v>-8.379884357739499</v>
+        <v>-9.872007486318866</v>
       </c>
       <c r="F51">
-        <v>-1.434719426473811</v>
+        <v>-0.2920455180718561</v>
       </c>
       <c r="G51">
-        <v>2.673463005025506</v>
+        <v>1.874873346769275</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.402973875468748</v>
       </c>
       <c r="E52">
-        <v>-9.174251154269003</v>
+        <v>-9.413979511287055</v>
       </c>
       <c r="F52">
-        <v>-1.325183198685399</v>
+        <v>-0.1851224050439196</v>
       </c>
       <c r="G52">
-        <v>2.001557992920565</v>
+        <v>2.392735364386388</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.574177609735808</v>
       </c>
       <c r="E53">
-        <v>-7.19288980779696</v>
+        <v>-8.165393186366192</v>
       </c>
       <c r="F53">
-        <v>-1.804697675762155</v>
+        <v>-0.1144511122733496</v>
       </c>
       <c r="G53">
-        <v>2.501837703178609</v>
+        <v>2.010506397513215</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.644934460070599</v>
       </c>
       <c r="E54">
-        <v>-5.912957385795003</v>
+        <v>-6.615948633797734</v>
       </c>
       <c r="F54">
-        <v>-1.528619725759089</v>
+        <v>0.1262405127551376</v>
       </c>
       <c r="G54">
-        <v>2.231809745722416</v>
+        <v>1.847855984623282</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.620419425562947</v>
       </c>
       <c r="E55">
-        <v>-7.144684201985309</v>
+        <v>-7.136528420297495</v>
       </c>
       <c r="F55">
-        <v>-1.576829317530981</v>
+        <v>0.2016969729492078</v>
       </c>
       <c r="G55">
-        <v>2.5682902837884</v>
+        <v>0.9437956560314102</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.508275399452996</v>
       </c>
       <c r="E56">
-        <v>-5.42845595171435</v>
+        <v>-7.054472471278507</v>
       </c>
       <c r="F56">
-        <v>-1.357028357233055</v>
+        <v>-0.4077281085180883</v>
       </c>
       <c r="G56">
-        <v>1.868874638252115</v>
+        <v>1.695448399631855</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.318602058296432</v>
       </c>
       <c r="E57">
-        <v>-5.786060487152064</v>
+        <v>-6.301088364518421</v>
       </c>
       <c r="F57">
-        <v>-1.932128988542075</v>
+        <v>-0.212331264524127</v>
       </c>
       <c r="G57">
-        <v>1.008768422785147</v>
+        <v>0.5975788035344295</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.063676077683518</v>
       </c>
       <c r="E58">
-        <v>-6.104403152943275</v>
+        <v>-4.783438227957816</v>
       </c>
       <c r="F58">
-        <v>-1.526195072002551</v>
+        <v>-0.1698238059007745</v>
       </c>
       <c r="G58">
-        <v>1.15242623591628</v>
+        <v>0.8931741041904145</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.755771828416756</v>
       </c>
       <c r="E59">
-        <v>-4.762761215638793</v>
+        <v>-4.086673631715632</v>
       </c>
       <c r="F59">
-        <v>-1.785743091513218</v>
+        <v>-0.3534465882664012</v>
       </c>
       <c r="G59">
-        <v>1.091522129630308</v>
+        <v>0.5268357559057435</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.410221088785927</v>
       </c>
       <c r="E60">
-        <v>-5.195244068793335</v>
+        <v>-6.521511836841776</v>
       </c>
       <c r="F60">
-        <v>-1.543672058632383</v>
+        <v>-0.4813134201730668</v>
       </c>
       <c r="G60">
-        <v>0.4707551144704896</v>
+        <v>0.6761910179099632</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.041417521154993</v>
       </c>
       <c r="E61">
-        <v>-3.995379595720997</v>
+        <v>-4.881688000028232</v>
       </c>
       <c r="F61">
-        <v>-2.038709229239319</v>
+        <v>-0.7070912865958607</v>
       </c>
       <c r="G61">
-        <v>1.355736769119542</v>
+        <v>1.12299217552662</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.661861515743181</v>
       </c>
       <c r="E62">
-        <v>-3.58469681643938</v>
+        <v>-3.759441571447364</v>
       </c>
       <c r="F62">
-        <v>-1.681547120071668</v>
+        <v>-0.7271980168982799</v>
       </c>
       <c r="G62">
-        <v>0.3409022762381166</v>
+        <v>-0.1746390489559676</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.288078043692196</v>
       </c>
       <c r="E63">
-        <v>-4.752966126360202</v>
+        <v>-4.796113426705285</v>
       </c>
       <c r="F63">
-        <v>-1.893059755461141</v>
+        <v>-0.66501380412855</v>
       </c>
       <c r="G63">
-        <v>0.4937137477853353</v>
+        <v>-0.4607397050053229</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.932390739065968</v>
       </c>
       <c r="E64">
-        <v>-3.480279262770517</v>
+        <v>-4.016047551092004</v>
       </c>
       <c r="F64">
-        <v>-2.019073651446742</v>
+        <v>-0.7415060079913176</v>
       </c>
       <c r="G64">
-        <v>-0.1934694319833421</v>
+        <v>-0.4093401749625984</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.6050487901446877</v>
       </c>
       <c r="E65">
-        <v>-3.434514504449</v>
+        <v>-4.449404399730027</v>
       </c>
       <c r="F65">
-        <v>-1.766429006021476</v>
+        <v>-0.3641160150187168</v>
       </c>
       <c r="G65">
-        <v>0.4463497727549824</v>
+        <v>-0.8737468137570997</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.3189120019942101</v>
       </c>
       <c r="E66">
-        <v>-3.146023539316352</v>
+        <v>-3.920175227875616</v>
       </c>
       <c r="F66">
-        <v>-2.035166479106481</v>
+        <v>-0.8449528865348646</v>
       </c>
       <c r="G66">
-        <v>-0.2085721407334973</v>
+        <v>-0.9954192939619337</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.08026175133676945</v>
       </c>
       <c r="E67">
-        <v>-2.477507563934016</v>
+        <v>-3.32770138803008</v>
       </c>
       <c r="F67">
-        <v>-2.033896346962298</v>
+        <v>-0.4170925615960817</v>
       </c>
       <c r="G67">
-        <v>-0.7760095778011965</v>
+        <v>-1.215795689420138</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.1076185346434736</v>
       </c>
       <c r="E68">
-        <v>-2.302943947886339</v>
+        <v>-3.12394722852896</v>
       </c>
       <c r="F68">
-        <v>-2.196071000115128</v>
+        <v>-1.312158801236825</v>
       </c>
       <c r="G68">
-        <v>-0.7171447675674155</v>
+        <v>-1.384150172274235</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.2420252623463267</v>
       </c>
       <c r="E69">
-        <v>-2.357158838706169</v>
+        <v>-3.130318791457752</v>
       </c>
       <c r="F69">
-        <v>-2.31032667153155</v>
+        <v>-1.396567159117917</v>
       </c>
       <c r="G69">
-        <v>-0.1866463976269042</v>
+        <v>-0.7205877349282576</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.3268611778261218</v>
       </c>
       <c r="E70">
-        <v>-2.368086046486678</v>
+        <v>-2.560328825060299</v>
       </c>
       <c r="F70">
-        <v>-2.420939027489502</v>
+        <v>-1.044153792137712</v>
       </c>
       <c r="G70">
-        <v>-0.3068986537953908</v>
+        <v>-1.776787494322876</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.3674544870740817</v>
       </c>
       <c r="E71">
-        <v>-1.949972041358473</v>
+        <v>-1.440491544651512</v>
       </c>
       <c r="F71">
-        <v>-2.503918882634868</v>
+        <v>-0.8379576575063685</v>
       </c>
       <c r="G71">
-        <v>-0.3938633745665056</v>
+        <v>-1.594982264942721</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.369640744215714</v>
       </c>
       <c r="E72">
-        <v>-3.269238788591056</v>
+        <v>-3.760215940502675</v>
       </c>
       <c r="F72">
-        <v>-2.308046135013317</v>
+        <v>-0.6836896561363697</v>
       </c>
       <c r="G72">
-        <v>-0.7823592041455186</v>
+        <v>-1.19389312013232</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.3426632239471297</v>
       </c>
       <c r="E73">
-        <v>-2.475007846281782</v>
+        <v>-2.956448031933248</v>
       </c>
       <c r="F73">
-        <v>-2.3954231496329</v>
+        <v>-1.405466794509729</v>
       </c>
       <c r="G73">
-        <v>-0.1085473178099576</v>
+        <v>0.06021767269100898</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.2949207752060945</v>
       </c>
       <c r="E74">
-        <v>-4.204522639291245</v>
+        <v>-3.240922240621093</v>
       </c>
       <c r="F74">
-        <v>-2.368170738240018</v>
+        <v>-1.301970821082803</v>
       </c>
       <c r="G74">
-        <v>0.1957447859776928</v>
+        <v>0.1568856024377276</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.2344502112993833</v>
       </c>
       <c r="E75">
-        <v>-3.702486953852894</v>
+        <v>-3.759287603331103</v>
       </c>
       <c r="F75">
-        <v>-2.444817353429541</v>
+        <v>-1.462100118045843</v>
       </c>
       <c r="G75">
-        <v>0.5075087910474784</v>
+        <v>-0.9521041161261095</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.168987114747749</v>
       </c>
       <c r="E76">
-        <v>-3.852103206592315</v>
+        <v>-2.905412129866804</v>
       </c>
       <c r="F76">
-        <v>-2.906264121570006</v>
+        <v>-1.745155084459378</v>
       </c>
       <c r="G76">
-        <v>0.1687572187415541</v>
+        <v>-0.01847068423192787</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.1041443030316573</v>
       </c>
       <c r="E77">
-        <v>-3.510307573915379</v>
+        <v>-5.644776626586756</v>
       </c>
       <c r="F77">
-        <v>-3.066092514409112</v>
+        <v>-1.872835039068022</v>
       </c>
       <c r="G77">
-        <v>0.6725792127266182</v>
+        <v>-0.2900479770005004</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.04449469811907144</v>
       </c>
       <c r="E78">
-        <v>-4.111747792296103</v>
+        <v>-5.445324517392923</v>
       </c>
       <c r="F78">
-        <v>-2.765133752621535</v>
+        <v>-1.717760931387064</v>
       </c>
       <c r="G78">
-        <v>0.7870214614736839</v>
+        <v>-0.3657899483934859</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.006449363826772283</v>
       </c>
       <c r="E79">
-        <v>-4.920682689708282</v>
+        <v>-6.575396149059046</v>
       </c>
       <c r="F79">
-        <v>-2.987141607112625</v>
+        <v>-1.399013192904313</v>
       </c>
       <c r="G79">
-        <v>-0.1761718315406501</v>
+        <v>-0.6632192912782272</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.04568018103419184</v>
       </c>
       <c r="E80">
-        <v>-5.278468364106301</v>
+        <v>-6.308655444585238</v>
       </c>
       <c r="F80">
-        <v>-2.644975609258271</v>
+        <v>-2.018079875984804</v>
       </c>
       <c r="G80">
-        <v>0.72167460307401</v>
+        <v>0.7000368774293335</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.0688985046201204</v>
       </c>
       <c r="E81">
-        <v>-6.441172179471696</v>
+        <v>-6.358830936590226</v>
       </c>
       <c r="F81">
-        <v>-3.407913264373901</v>
+        <v>-2.012625592812031</v>
       </c>
       <c r="G81">
-        <v>1.774378426379158</v>
+        <v>0.9584547516793031</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.07245873109540406</v>
       </c>
       <c r="E82">
-        <v>-7.327679836635268</v>
+        <v>-7.337592666238058</v>
       </c>
       <c r="F82">
-        <v>-3.146958914010324</v>
+        <v>-1.957023261826867</v>
       </c>
       <c r="G82">
-        <v>1.296140328321582</v>
+        <v>1.112474572348356</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.05185110601986388</v>
       </c>
       <c r="E83">
-        <v>-7.909701958471101</v>
+        <v>-8.343203718277369</v>
       </c>
       <c r="F83">
-        <v>-3.437317932105865</v>
+        <v>-2.264727818961259</v>
       </c>
       <c r="G83">
-        <v>1.177195737641108</v>
+        <v>0.5861243159685512</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.0006176553966388935</v>
       </c>
       <c r="E84">
-        <v>-10.300115833582</v>
+        <v>-9.24753997760914</v>
       </c>
       <c r="F84">
-        <v>-3.364438953289173</v>
+        <v>-2.27263130333226</v>
       </c>
       <c r="G84">
-        <v>1.535972799914083</v>
+        <v>1.642476360457976</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.08529470762376312</v>
       </c>
       <c r="E85">
-        <v>-11.42374797520921</v>
+        <v>-10.96845972695204</v>
       </c>
       <c r="F85">
-        <v>-3.344528602520268</v>
+        <v>-2.171054781474847</v>
       </c>
       <c r="G85">
-        <v>1.266749305023932</v>
+        <v>1.374603568147848</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.2111645229400192</v>
       </c>
       <c r="E86">
-        <v>-11.92668482697509</v>
+        <v>-11.91069931372802</v>
       </c>
       <c r="F86">
-        <v>-3.347660380968049</v>
+        <v>-1.842587047936086</v>
       </c>
       <c r="G86">
-        <v>1.726094119688888</v>
+        <v>1.977940561043404</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3834892936082914</v>
       </c>
       <c r="E87">
-        <v>-12.44894014885769</v>
+        <v>-12.86919612219152</v>
       </c>
       <c r="F87">
-        <v>-3.988697816213433</v>
+        <v>-2.396626766128634</v>
       </c>
       <c r="G87">
-        <v>2.280196679324403</v>
+        <v>1.896901716787585</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6037409552184921</v>
       </c>
       <c r="E88">
-        <v>-14.57238236732039</v>
+        <v>-14.98000389817282</v>
       </c>
       <c r="F88">
-        <v>-3.64377379450734</v>
+        <v>-2.445248913291498</v>
       </c>
       <c r="G88">
-        <v>2.16769441026335</v>
+        <v>2.501036551158105</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8754611984690404</v>
       </c>
       <c r="E89">
-        <v>-16.02135819555468</v>
+        <v>-15.71370272842157</v>
       </c>
       <c r="F89">
-        <v>-3.659749427929336</v>
+        <v>-2.798665557969134</v>
       </c>
       <c r="G89">
-        <v>2.388660082827545</v>
+        <v>1.819468056624032</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.201828893363128</v>
       </c>
       <c r="E90">
-        <v>-17.29520887696433</v>
+        <v>-17.34906601833756</v>
       </c>
       <c r="F90">
-        <v>-4.014298422336511</v>
+        <v>-2.182745698542621</v>
       </c>
       <c r="G90">
-        <v>1.58972281728969</v>
+        <v>2.126855520490901</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.577684940066049</v>
       </c>
       <c r="E91">
-        <v>-18.65621456912561</v>
+        <v>-19.99016715756507</v>
       </c>
       <c r="F91">
-        <v>-3.611913590753487</v>
+        <v>-2.364137039273393</v>
       </c>
       <c r="G91">
-        <v>1.783277172788719</v>
+        <v>1.212165030172429</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.001896038912077</v>
       </c>
       <c r="E92">
-        <v>-20.85153725551206</v>
+        <v>-21.12790549572617</v>
       </c>
       <c r="F92">
-        <v>-3.735185299946505</v>
+        <v>-2.490605458856726</v>
       </c>
       <c r="G92">
-        <v>1.744888086715331</v>
+        <v>1.236967637352649</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.470184993558604</v>
       </c>
       <c r="E93">
-        <v>-24.11306650463446</v>
+        <v>-23.28460482730121</v>
       </c>
       <c r="F93">
-        <v>-3.771652504208372</v>
+        <v>-2.483274484174157</v>
       </c>
       <c r="G93">
-        <v>0.4697189137166977</v>
+        <v>1.640288089856518</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.96793275004852</v>
       </c>
       <c r="E94">
-        <v>-24.92872618594803</v>
+        <v>-25.62775501919405</v>
       </c>
       <c r="F94">
-        <v>-4.159006382947959</v>
+        <v>-2.652864048423075</v>
       </c>
       <c r="G94">
-        <v>1.330169425919751</v>
+        <v>0.7637814317880002</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.48741830099786</v>
       </c>
       <c r="E95">
-        <v>-26.89879351824494</v>
+        <v>-27.87596122504208</v>
       </c>
       <c r="F95">
-        <v>-4.005032159025275</v>
+        <v>-3.052467892418587</v>
       </c>
       <c r="G95">
-        <v>0.8672426009813033</v>
+        <v>0.9495560052697422</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.01547789817909</v>
       </c>
       <c r="E96">
-        <v>-29.97782752909523</v>
+        <v>-30.15259039799924</v>
       </c>
       <c r="F96">
-        <v>-3.673531628658447</v>
+        <v>-3.183323177387686</v>
       </c>
       <c r="G96">
-        <v>0.9625465859658423</v>
+        <v>0.4930781230417952</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.530711872711589</v>
       </c>
       <c r="E97">
-        <v>-31.88804428466977</v>
+        <v>-31.6925296836256</v>
       </c>
       <c r="F97">
-        <v>-4.413512674676825</v>
+        <v>-2.426508129341145</v>
       </c>
       <c r="G97">
-        <v>0.3614905589468441</v>
+        <v>0.8596051724222047</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.021264709757932</v>
       </c>
       <c r="E98">
-        <v>-33.71049015702764</v>
+        <v>-33.86391485640751</v>
       </c>
       <c r="F98">
-        <v>-3.919632401241118</v>
+        <v>-3.233204370753325</v>
       </c>
       <c r="G98">
-        <v>0.0002736246114255948</v>
+        <v>0.2221132811979878</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.468651523041587</v>
       </c>
       <c r="E99">
-        <v>-37.63090331731806</v>
+        <v>-37.27690118295344</v>
       </c>
       <c r="F99">
-        <v>-4.133073198582639</v>
+        <v>-2.941915717285421</v>
       </c>
       <c r="G99">
-        <v>0.108548327018829</v>
+        <v>0.1370388819297969</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.853168566137278</v>
       </c>
       <c r="E100">
-        <v>-39.06841531360192</v>
+        <v>-39.71385871391518</v>
       </c>
       <c r="F100">
-        <v>-4.442611687167109</v>
+        <v>-3.566892790842332</v>
       </c>
       <c r="G100">
-        <v>-0.8119753445398387</v>
+        <v>0.05024962007226343</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.159664364128893</v>
       </c>
       <c r="E101">
-        <v>-41.49763368248455</v>
+        <v>-42.51559161890577</v>
       </c>
       <c r="F101">
-        <v>-4.539676230871436</v>
+        <v>-3.162906040725841</v>
       </c>
       <c r="G101">
-        <v>-1.111473778386624</v>
+        <v>-1.108298965214463</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.375840977473709</v>
       </c>
       <c r="E102">
-        <v>-44.12448371400993</v>
+        <v>-46.2330340456984</v>
       </c>
       <c r="F102">
-        <v>-4.558783642741212</v>
+        <v>-3.274645203442629</v>
       </c>
       <c r="G102">
-        <v>-1.93825273190975</v>
+        <v>-1.073614379599519</v>
       </c>
     </row>
   </sheetData>
